--- a/data/trans_orig/IP07A13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39316</t>
+          <t>39178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>41955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>33410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>48340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67013</t>
+          <t>66752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>86056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32292</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48355</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50440</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71992</t>
+          <t>71972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93224</t>
+          <t>94213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>47198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62496</t>
+          <t>62975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38559</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54125</t>
+          <t>53367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90626</t>
+          <t>88877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112537</t>
+          <t>110862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>30378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46643</t>
+          <t>46555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37685</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60568</t>
+          <t>60860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78168</t>
+          <t>78684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>25228</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33591</t>
+          <t>34058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>50137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>28368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67112</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89263</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44054</t>
+          <t>43848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47562</t>
+          <t>48139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>63108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>80690</t>
+          <t>80542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102857</t>
+          <t>103995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>112011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>139940</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115134</t>
+          <t>114200</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142308</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>233703</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>273662</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>141788</t>
+          <t>143450</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171510</t>
+          <t>172180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>166959</t>
+          <t>167474</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>194767</t>
+          <t>197175</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>317405</t>
+          <t>319018</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>361235</t>
+          <t>359750</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44791</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27191</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>33579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>38051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55552</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>34109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35597</t>
+          <t>35045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49121</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74242</t>
+          <t>74355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94432</t>
+          <t>92743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>30418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26552</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42102</t>
+          <t>41863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>82541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40452</t>
+          <t>40425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56629</t>
+          <t>56709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>39786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55035</t>
+          <t>54836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84452</t>
+          <t>84523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>106486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>19005</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67693</t>
+          <t>68053</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44068</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53543</t>
+          <t>53588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>71702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39497</t>
+          <t>39927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>47159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63451</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>53819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89598</t>
+          <t>89688</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112557</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,47 +6809,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>7824</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>117215</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>115467</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143773</t>
+          <t>144513</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>214992</t>
+          <t>214694</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>254501</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>169633</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>198426</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>145291</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171993</t>
+          <t>174990</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>321210</t>
+          <t>322979</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>363247</t>
+          <t>364575</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70958</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>62473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84530</t>
+          <t>83733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>28346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42230</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>34106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>50926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71088</t>
+          <t>71622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>44072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59248</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50499</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67945</t>
+          <t>68599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100481</t>
+          <t>99457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123585</t>
+          <t>123899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46220</t>
+          <t>46085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>72186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94751</t>
+          <t>96065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36092</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50355</t>
+          <t>49523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72622</t>
+          <t>72489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92064</t>
+          <t>91725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>34969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>35922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46896</t>
+          <t>46710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66488</t>
+          <t>65760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60367</t>
+          <t>60581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38735</t>
+          <t>39595</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>56196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85850</t>
+          <t>88705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111708</t>
+          <t>111808</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37979</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55719</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37793</t>
+          <t>37292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55078</t>
+          <t>54138</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79695</t>
+          <t>79999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103976</t>
+          <t>102815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>157612</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190398</t>
+          <t>187861</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>176908</t>
+          <t>179298</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>209545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>342511</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>390059</t>
+          <t>390229</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171255</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>123327</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154751</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>270164</t>
+          <t>272051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>313949</t>
+          <t>315585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
